--- a/docs/requirement_analysis/要件定義.xlsx
+++ b/docs/requirement_analysis/要件定義.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\rde2\gitlab\RDE_XPS\docs\requirement_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\rde2\gitlab\xps\docs\requirement_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333912D7-4233-488F-BB0F-5CF9D609D32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1466D59-1F44-47AE-AE9D-262C6ADB79B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要件定義（手入力 メタデータ項目リスト）_bak" sheetId="15" state="hidden" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="778">
   <si>
     <t>仕様として固定されている項目</t>
     <rPh sb="0" eb="2">
@@ -1562,6 +1562,13 @@
   </si>
   <si>
     <t>Sample type</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>高田</t>
+    <rPh sb="0" eb="2">
+      <t>タカダ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3515,9 +3522,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>元素毎のCountデータのプロット</t>
-  </si>
-  <si>
     <t>元素分、出力される。
 計測データのX軸ラベルに'.reverse'が付与されていた場合、X軸を反転させる。</t>
   </si>
@@ -3555,9 +3559,6 @@
     <t>全元素のスパッタリング時間に対するCPSデータのプロット</t>
   </si>
   <si>
-    <t>全元素のスパッタリング時間に対するCountデータのプロット</t>
-  </si>
-  <si>
     <t>全元素の入射角に対する光電子の強さ</t>
   </si>
   <si>
@@ -3583,7 +3584,15 @@
     <t>全元素の入射角毎に対するCountデータのプロット</t>
   </si>
   <si>
-    <t>NIMS</t>
+    <t>全元素のスパッタリング時間に対するCountデータのプロット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全素毎のCountデータのプロット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>XPS_count.csv</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5756,50 +5765,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>268653</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>317500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2829021</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>2210288</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69AC7F8F-2050-79E0-6C0E-3F3357A7D5B4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8425961" y="17108365"/>
-          <a:ext cx="2560368" cy="1892788"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
       <xdr:colOff>2808654</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>561731</xdr:rowOff>
@@ -5824,7 +5789,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5868,7 +5833,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5912,7 +5877,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5956,7 +5921,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6000,7 +5965,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6044,7 +6009,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6088,7 +6053,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6132,7 +6097,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6176,7 +6141,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6220,7 +6185,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6264,7 +6229,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6308,7 +6273,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6352,7 +6317,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6361,6 +6326,50 @@
         <a:xfrm>
           <a:off x="8316058" y="41897790"/>
           <a:ext cx="5373077" cy="925320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>268655</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>341923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2735384</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2191970</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{125F2689-10EE-06C8-57E1-0BE4C6C6DC04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8425963" y="17132788"/>
+          <a:ext cx="2466729" cy="1850047"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10464,7 +10473,7 @@
         <v>278</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -10541,14 +10550,14 @@
       <c r="J11" s="15"/>
       <c r="K11" s="97"/>
       <c r="L11" s="97" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="212"/>
       <c r="B12" s="212"/>
       <c r="C12" s="91" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
@@ -10869,99 +10878,99 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="201" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B26" s="197" t="s">
         <v>275</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D26" s="125"/>
       <c r="E26" s="125"/>
       <c r="F26" s="126" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G26" s="126" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H26" s="32" t="s">
         <v>200</v>
       </c>
       <c r="I26" s="126" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J26" s="38"/>
       <c r="K26" s="127"/>
       <c r="L26" s="127" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="201"/>
       <c r="B27" s="198"/>
       <c r="C27" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D27" s="125"/>
       <c r="E27" s="125"/>
       <c r="F27" s="126" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G27" s="126" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>200</v>
       </c>
       <c r="I27" s="126" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J27" s="38"/>
       <c r="K27" s="127"/>
       <c r="L27" s="127" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="201"/>
       <c r="B28" s="198"/>
       <c r="C28" s="21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D28" s="125"/>
       <c r="E28" s="125"/>
       <c r="F28" s="126" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G28" s="126" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H28" s="32" t="s">
         <v>200</v>
       </c>
       <c r="I28" s="126" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J28" s="38"/>
       <c r="K28" s="127"/>
       <c r="L28" s="127" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="201"/>
       <c r="B29" s="198"/>
       <c r="C29" s="21" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D29" s="125"/>
       <c r="E29" s="125"/>
       <c r="F29" s="126" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G29" s="126" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H29" s="32" t="s">
         <v>21</v>
@@ -10969,25 +10978,25 @@
       <c r="I29" s="126"/>
       <c r="J29" s="38"/>
       <c r="K29" s="127" t="s">
+        <v>358</v>
+      </c>
+      <c r="L29" s="127" t="s">
         <v>357</v>
-      </c>
-      <c r="L29" s="127" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="201"/>
       <c r="B30" s="198"/>
       <c r="C30" s="21" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D30" s="125"/>
       <c r="E30" s="125"/>
       <c r="F30" s="126" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G30" s="126" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H30" s="32" t="s">
         <v>21</v>
@@ -10995,25 +11004,25 @@
       <c r="I30" s="126"/>
       <c r="J30" s="38"/>
       <c r="K30" s="127" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L30" s="127" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="201"/>
       <c r="B31" s="198"/>
       <c r="C31" s="21" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D31" s="125"/>
       <c r="E31" s="125"/>
       <c r="F31" s="126" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G31" s="126" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H31" s="32" t="s">
         <v>21</v>
@@ -11021,27 +11030,27 @@
       <c r="I31" s="126"/>
       <c r="J31" s="38"/>
       <c r="K31" s="127" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L31" s="127" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="201"/>
       <c r="B32" s="198"/>
       <c r="C32" s="21" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D32" s="125" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="125"/>
       <c r="F32" s="126" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G32" s="126" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H32" s="32" t="s">
         <v>200</v>
@@ -11049,10 +11058,10 @@
       <c r="I32" s="126"/>
       <c r="J32" s="38"/>
       <c r="K32" s="128" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L32" s="127" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -11086,10 +11095,10 @@
       <c r="D34" s="31"/>
       <c r="E34" s="31"/>
       <c r="F34" s="32" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G34" s="32" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H34" s="21" t="s">
         <v>21</v>
@@ -11108,10 +11117,10 @@
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
       <c r="F35" s="32" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G35" s="32" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H35" s="21" t="s">
         <v>21</v>
@@ -11133,7 +11142,7 @@
         <v>85</v>
       </c>
       <c r="G36" s="32" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H36" s="21" t="s">
         <v>21</v>
@@ -11155,7 +11164,7 @@
         <v>87</v>
       </c>
       <c r="G37" s="32" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H37" s="21" t="s">
         <v>21</v>
@@ -11188,7 +11197,7 @@
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
       <c r="K38" s="24" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L38" s="24"/>
       <c r="N38" s="37"/>
@@ -11292,7 +11301,7 @@
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
       <c r="K42" s="110" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L42" s="111"/>
       <c r="N42" s="37"/>
@@ -11318,7 +11327,7 @@
       <c r="I43" s="38"/>
       <c r="J43" s="38"/>
       <c r="K43" s="110" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L43" s="111"/>
       <c r="N43" s="37"/>
@@ -11368,7 +11377,7 @@
       <c r="I45" s="38"/>
       <c r="J45" s="38"/>
       <c r="K45" s="41" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L45" s="41"/>
       <c r="N45" s="37"/>
@@ -11418,10 +11427,10 @@
       <c r="I47" s="123"/>
       <c r="J47" s="123"/>
       <c r="K47" s="124" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L47" s="119" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N47" s="37"/>
     </row>
@@ -11575,7 +11584,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="93.75">
@@ -11613,7 +11622,7 @@
         <v>16</v>
       </c>
       <c r="L2" s="136" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M2" s="47" t="s">
         <v>139</v>
@@ -11622,23 +11631,23 @@
     <row r="3" spans="1:13" ht="19.5">
       <c r="A3" s="94"/>
       <c r="B3" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C3" s="134" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D3" s="98" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E3" s="129"/>
       <c r="F3" s="131" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G3" s="131" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H3" s="135" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I3" s="134"/>
       <c r="J3" s="98"/>
@@ -11649,10 +11658,10 @@
     <row r="4" spans="1:13" ht="19.5">
       <c r="A4" s="94"/>
       <c r="B4" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C4" s="134" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D4" s="98"/>
       <c r="E4" s="129"/>
@@ -11674,15 +11683,15 @@
     <row r="5" spans="1:13" ht="19.5">
       <c r="A5" s="94"/>
       <c r="B5" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D5" s="98"/>
       <c r="E5" s="129"/>
       <c r="F5" s="131" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G5" s="131" t="s">
         <v>279</v>
@@ -11699,20 +11708,20 @@
     <row r="6" spans="1:13" ht="19.5">
       <c r="A6" s="94"/>
       <c r="B6" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D6" s="98" t="s">
         <v>298</v>
       </c>
       <c r="E6" s="129"/>
       <c r="F6" s="131" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G6" s="131" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H6" s="135" t="s">
         <v>27</v>
@@ -11726,18 +11735,18 @@
     <row r="7" spans="1:13" ht="19.5">
       <c r="A7" s="94"/>
       <c r="B7" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D7" s="98"/>
       <c r="E7" s="129"/>
       <c r="F7" s="131" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G7" s="131" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H7" s="135" t="s">
         <v>27</v>
@@ -11751,20 +11760,20 @@
     <row r="8" spans="1:13" ht="19.5">
       <c r="A8" s="94"/>
       <c r="B8" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D8" s="98" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E8" s="129"/>
       <c r="F8" s="131" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G8" s="131" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H8" s="135" t="s">
         <v>27</v>
@@ -11778,20 +11787,20 @@
     <row r="9" spans="1:13" ht="19.5">
       <c r="A9" s="94"/>
       <c r="B9" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D9" s="98" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E9" s="129"/>
       <c r="F9" s="131" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G9" s="131" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H9" s="135" t="s">
         <v>27</v>
@@ -11805,20 +11814,20 @@
     <row r="10" spans="1:13" ht="19.5">
       <c r="A10" s="94"/>
       <c r="B10" s="132" t="s">
+        <v>518</v>
+      </c>
+      <c r="C10" s="134" t="s">
+        <v>469</v>
+      </c>
+      <c r="D10" s="98" t="s">
         <v>517</v>
-      </c>
-      <c r="C10" s="134" t="s">
-        <v>468</v>
-      </c>
-      <c r="D10" s="98" t="s">
-        <v>516</v>
       </c>
       <c r="E10" s="129"/>
       <c r="F10" s="131" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G10" s="131" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H10" s="135" t="s">
         <v>27</v>
@@ -11832,20 +11841,20 @@
     <row r="11" spans="1:13" ht="19.5">
       <c r="A11" s="94"/>
       <c r="B11" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D11" s="98" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E11" s="129"/>
       <c r="F11" s="131" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G11" s="131" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H11" s="135" t="s">
         <v>27</v>
@@ -11859,20 +11868,20 @@
     <row r="12" spans="1:13" ht="19.5">
       <c r="A12" s="94"/>
       <c r="B12" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D12" s="98" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E12" s="129"/>
       <c r="F12" s="131" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G12" s="131" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H12" s="135" t="s">
         <v>27</v>
@@ -11886,26 +11895,26 @@
     <row r="13" spans="1:13" ht="37.5">
       <c r="A13" s="94"/>
       <c r="B13" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C13" s="180" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D13" s="181" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E13" s="182"/>
       <c r="F13" s="183" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G13" s="183" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H13" s="184" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="180" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J13" s="181"/>
       <c r="K13" s="177"/>
@@ -11915,20 +11924,20 @@
     <row r="14" spans="1:13" ht="19.5">
       <c r="A14" s="94"/>
       <c r="B14" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D14" s="98" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E14" s="129"/>
       <c r="F14" s="131" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G14" s="131" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H14" s="135" t="s">
         <v>27</v>
@@ -11944,20 +11953,20 @@
     <row r="15" spans="1:13" ht="39">
       <c r="A15" s="94"/>
       <c r="B15" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C15" s="180" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D15" s="181" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="182"/>
       <c r="F15" s="183" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G15" s="183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H15" s="184" t="s">
         <v>27</v>
@@ -11971,20 +11980,20 @@
     <row r="16" spans="1:13" ht="39">
       <c r="A16" s="94"/>
       <c r="B16" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C16" s="180" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D16" s="181" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E16" s="182"/>
       <c r="F16" s="183" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G16" s="183" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H16" s="184" t="s">
         <v>27</v>
@@ -11998,26 +12007,26 @@
     <row r="17" spans="1:13" ht="39">
       <c r="A17" s="94"/>
       <c r="B17" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C17" s="180" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D17" s="181" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E17" s="182"/>
       <c r="F17" s="183" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G17" s="183" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H17" s="184" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="180" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J17" s="181"/>
       <c r="K17" s="177"/>
@@ -12027,18 +12036,18 @@
     <row r="18" spans="1:13" ht="19.5">
       <c r="A18" s="94"/>
       <c r="B18" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C18" s="134" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D18" s="98"/>
       <c r="E18" s="129"/>
       <c r="F18" s="131" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G18" s="131" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H18" s="135" t="s">
         <v>27</v>
@@ -12052,18 +12061,18 @@
     <row r="19" spans="1:13" ht="19.5">
       <c r="A19" s="94"/>
       <c r="B19" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C19" s="134" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D19" s="98"/>
       <c r="E19" s="129"/>
       <c r="F19" s="131" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G19" s="131" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H19" s="135" t="s">
         <v>27</v>
@@ -12079,18 +12088,18 @@
     <row r="20" spans="1:13" ht="39">
       <c r="A20" s="94"/>
       <c r="B20" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C20" s="180" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D20" s="181"/>
       <c r="E20" s="182"/>
       <c r="F20" s="183" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G20" s="183" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H20" s="184" t="s">
         <v>27</v>
@@ -12106,24 +12115,24 @@
     <row r="21" spans="1:13" ht="39">
       <c r="A21" s="94"/>
       <c r="B21" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C21" s="180" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D21" s="181"/>
       <c r="E21" s="182"/>
       <c r="F21" s="183" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G21" s="183" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H21" s="184" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="180" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J21" s="181"/>
       <c r="K21" s="177"/>
@@ -12135,18 +12144,18 @@
     <row r="22" spans="1:13" ht="39">
       <c r="A22" s="94"/>
       <c r="B22" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C22" s="180" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D22" s="181"/>
       <c r="E22" s="182"/>
       <c r="F22" s="183" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G22" s="183" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H22" s="184" t="s">
         <v>27</v>
@@ -12162,24 +12171,24 @@
     <row r="23" spans="1:13" ht="19.5">
       <c r="A23" s="94"/>
       <c r="B23" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D23" s="98"/>
       <c r="E23" s="129"/>
       <c r="F23" s="131" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G23" s="131" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H23" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I23" s="134" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J23" s="98"/>
       <c r="K23" s="50"/>
@@ -12191,24 +12200,24 @@
     <row r="24" spans="1:13" ht="19.5">
       <c r="A24" s="94"/>
       <c r="B24" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C24" s="134" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D24" s="98"/>
       <c r="E24" s="129"/>
       <c r="F24" s="131" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G24" s="131" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H24" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I24" s="134" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J24" s="98"/>
       <c r="K24" s="50"/>
@@ -12220,24 +12229,24 @@
     <row r="25" spans="1:13" ht="19.5">
       <c r="A25" s="94"/>
       <c r="B25" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C25" s="134" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D25" s="98"/>
       <c r="E25" s="129"/>
       <c r="F25" s="131" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G25" s="131" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H25" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I25" s="134" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J25" s="98"/>
       <c r="K25" s="50"/>
@@ -12249,20 +12258,20 @@
     <row r="26" spans="1:13" ht="19.5">
       <c r="A26" s="94"/>
       <c r="B26" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C26" s="134" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D26" s="98" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E26" s="129"/>
       <c r="F26" s="131" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G26" s="131" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H26" s="135" t="s">
         <v>27</v>
@@ -12278,18 +12287,18 @@
     <row r="27" spans="1:13" ht="19.5">
       <c r="A27" s="94"/>
       <c r="B27" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C27" s="134" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D27" s="98"/>
       <c r="E27" s="129"/>
       <c r="F27" s="131" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G27" s="131" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H27" s="135" t="s">
         <v>27</v>
@@ -12305,26 +12314,26 @@
     <row r="28" spans="1:13" ht="19.5">
       <c r="A28" s="94"/>
       <c r="B28" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C28" s="134" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D28" s="98" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E28" s="129"/>
       <c r="F28" s="131" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G28" s="131" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H28" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I28" s="134" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J28" s="98"/>
       <c r="K28" s="50"/>
@@ -12336,26 +12345,26 @@
     <row r="29" spans="1:13" ht="19.5">
       <c r="A29" s="94"/>
       <c r="B29" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C29" s="134" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D29" s="98" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E29" s="129"/>
       <c r="F29" s="131" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G29" s="131" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H29" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="134" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J29" s="98"/>
       <c r="K29" s="50"/>
@@ -12367,26 +12376,26 @@
     <row r="30" spans="1:13" ht="19.5">
       <c r="A30" s="94"/>
       <c r="B30" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C30" s="134" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D30" s="98" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E30" s="129"/>
       <c r="F30" s="131" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G30" s="131" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H30" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I30" s="134" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J30" s="98"/>
       <c r="K30" s="50"/>
@@ -12398,26 +12407,26 @@
     <row r="31" spans="1:13" ht="19.5">
       <c r="A31" s="94"/>
       <c r="B31" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C31" s="134" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D31" s="98" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E31" s="129"/>
       <c r="F31" s="131" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G31" s="131" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H31" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I31" s="134" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J31" s="98"/>
       <c r="K31" s="50"/>
@@ -12429,26 +12438,26 @@
     <row r="32" spans="1:13" ht="37.5">
       <c r="A32" s="94"/>
       <c r="B32" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C32" s="134" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D32" s="98" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E32" s="129"/>
       <c r="F32" s="131" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G32" s="131" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H32" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I32" s="134" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J32" s="98"/>
       <c r="K32" s="50"/>
@@ -12460,20 +12469,20 @@
     <row r="33" spans="1:13" ht="39">
       <c r="A33" s="94"/>
       <c r="B33" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C33" s="134" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D33" s="98" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E33" s="129"/>
       <c r="F33" s="131" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G33" s="131" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H33" s="135" t="s">
         <v>27</v>
@@ -12489,20 +12498,20 @@
     <row r="34" spans="1:13" ht="19.5">
       <c r="A34" s="94"/>
       <c r="B34" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C34" s="134" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D34" s="98" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E34" s="129"/>
       <c r="F34" s="131" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G34" s="131" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H34" s="135" t="s">
         <v>27</v>
@@ -12518,20 +12527,20 @@
     <row r="35" spans="1:13" ht="19.5">
       <c r="A35" s="94"/>
       <c r="B35" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C35" s="134" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D35" s="98" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E35" s="129"/>
       <c r="F35" s="131" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G35" s="131" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H35" s="135" t="s">
         <v>27</v>
@@ -12547,20 +12556,20 @@
     <row r="36" spans="1:13" ht="19.5">
       <c r="A36" s="94"/>
       <c r="B36" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C36" s="134" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D36" s="98" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E36" s="129"/>
       <c r="F36" s="131" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G36" s="131" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H36" s="135" t="s">
         <v>27</v>
@@ -12576,26 +12585,26 @@
     <row r="37" spans="1:13" ht="19.5">
       <c r="A37" s="94"/>
       <c r="B37" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C37" s="134" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D37" s="98" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E37" s="129"/>
       <c r="F37" s="131" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G37" s="131" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H37" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I37" s="134" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J37" s="98"/>
       <c r="K37" s="50"/>
@@ -12607,18 +12616,18 @@
     <row r="38" spans="1:13" ht="19.5">
       <c r="A38" s="94"/>
       <c r="B38" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C38" s="134" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D38" s="98"/>
       <c r="E38" s="129"/>
       <c r="F38" s="131" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G38" s="131" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H38" s="135" t="s">
         <v>27</v>
@@ -12634,24 +12643,24 @@
     <row r="39" spans="1:13" ht="39">
       <c r="A39" s="94"/>
       <c r="B39" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C39" s="180" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D39" s="181"/>
       <c r="E39" s="182"/>
       <c r="F39" s="183" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G39" s="183" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H39" s="184" t="s">
         <v>27</v>
       </c>
       <c r="I39" s="180" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J39" s="181"/>
       <c r="K39" s="177"/>
@@ -12663,24 +12672,24 @@
     <row r="40" spans="1:13" ht="19.5">
       <c r="A40" s="94"/>
       <c r="B40" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C40" s="134" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D40" s="98"/>
       <c r="E40" s="129"/>
       <c r="F40" s="131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G40" s="131" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H40" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I40" s="134" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J40" s="98"/>
       <c r="K40" s="50"/>
@@ -12692,24 +12701,24 @@
     <row r="41" spans="1:13" ht="19.5">
       <c r="A41" s="94"/>
       <c r="B41" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C41" s="134" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D41" s="98"/>
       <c r="E41" s="129"/>
       <c r="F41" s="131" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G41" s="131" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H41" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I41" s="134" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J41" s="98"/>
       <c r="K41" s="50"/>
@@ -12721,26 +12730,26 @@
     <row r="42" spans="1:13" ht="19.5">
       <c r="A42" s="94"/>
       <c r="B42" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C42" s="134" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D42" s="98" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E42" s="129"/>
       <c r="F42" s="131" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G42" s="131" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H42" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I42" s="134" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J42" s="98"/>
       <c r="K42" s="50"/>
@@ -12752,24 +12761,24 @@
     <row r="43" spans="1:13" ht="39">
       <c r="A43" s="94"/>
       <c r="B43" s="179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C43" s="180" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D43" s="181"/>
       <c r="E43" s="182"/>
       <c r="F43" s="183" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G43" s="183" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H43" s="184" t="s">
         <v>27</v>
       </c>
       <c r="I43" s="180" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J43" s="181"/>
       <c r="K43" s="177"/>
@@ -12781,24 +12790,24 @@
     <row r="44" spans="1:13" ht="19.5">
       <c r="A44" s="94"/>
       <c r="B44" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C44" s="134" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D44" s="98"/>
       <c r="E44" s="129"/>
       <c r="F44" s="131" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G44" s="131" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H44" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I44" s="134" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J44" s="98"/>
       <c r="K44" s="50"/>
@@ -12810,20 +12819,20 @@
     <row r="45" spans="1:13" ht="19.5">
       <c r="A45" s="94"/>
       <c r="B45" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C45" s="134" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D45" s="98" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E45" s="129"/>
       <c r="F45" s="131" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G45" s="131" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H45" s="135" t="s">
         <v>27</v>
@@ -12839,26 +12848,26 @@
     <row r="46" spans="1:13" ht="19.5">
       <c r="A46" s="94"/>
       <c r="B46" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C46" s="134" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D46" s="98" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E46" s="129"/>
       <c r="F46" s="131" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G46" s="131" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H46" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I46" s="134" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J46" s="98"/>
       <c r="K46" s="50"/>
@@ -12870,26 +12879,26 @@
     <row r="47" spans="1:13" ht="19.5">
       <c r="A47" s="94"/>
       <c r="B47" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C47" s="134" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D47" s="98" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E47" s="129"/>
       <c r="F47" s="131" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G47" s="131" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H47" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I47" s="134" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J47" s="98"/>
       <c r="K47" s="50"/>
@@ -12901,26 +12910,26 @@
     <row r="48" spans="1:13" ht="19.5">
       <c r="A48" s="94"/>
       <c r="B48" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C48" s="134" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D48" s="98" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E48" s="129"/>
       <c r="F48" s="131" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G48" s="131" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H48" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I48" s="134" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J48" s="98"/>
       <c r="K48" s="50"/>
@@ -12932,18 +12941,18 @@
     <row r="49" spans="1:13" ht="19.5">
       <c r="A49" s="94"/>
       <c r="B49" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C49" s="134" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D49" s="98"/>
       <c r="E49" s="129"/>
       <c r="F49" s="131" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G49" s="131" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H49" s="135" t="s">
         <v>27</v>
@@ -12959,20 +12968,20 @@
     <row r="50" spans="1:13" ht="19.5">
       <c r="A50" s="94"/>
       <c r="B50" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C50" s="134" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D50" s="98" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E50" s="129"/>
       <c r="F50" s="131" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G50" s="131" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H50" s="135" t="s">
         <v>27</v>
@@ -12988,26 +12997,26 @@
     <row r="51" spans="1:13" ht="19.5">
       <c r="A51" s="94"/>
       <c r="B51" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C51" s="134" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D51" s="98" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E51" s="129"/>
       <c r="F51" s="131" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G51" s="131" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H51" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I51" s="134" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J51" s="98"/>
       <c r="K51" s="50"/>
@@ -13019,26 +13028,26 @@
     <row r="52" spans="1:13" ht="19.5">
       <c r="A52" s="94"/>
       <c r="B52" s="132" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C52" s="134" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D52" s="98" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E52" s="129"/>
       <c r="F52" s="131" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G52" s="131" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H52" s="135" t="s">
         <v>27</v>
       </c>
       <c r="I52" s="134" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J52" s="98"/>
       <c r="K52" s="50"/>
@@ -13050,20 +13059,20 @@
     <row r="53" spans="1:13" ht="20.25" thickBot="1">
       <c r="A53" s="165"/>
       <c r="B53" s="154" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C53" s="155" t="s">
         <v>148</v>
       </c>
       <c r="D53" s="156" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E53" s="157"/>
       <c r="F53" s="158" t="s">
         <v>150</v>
       </c>
       <c r="G53" s="158" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H53" s="159" t="s">
         <v>27</v>
@@ -13077,18 +13086,18 @@
     <row r="54" spans="1:13" ht="19.5">
       <c r="A54" s="166"/>
       <c r="B54" s="169" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C54" s="164" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="15"/>
       <c r="F54" s="13" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H54" s="15" t="s">
         <v>27</v>
@@ -13102,20 +13111,20 @@
     <row r="55" spans="1:13" ht="19.5">
       <c r="A55" s="94"/>
       <c r="B55" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C55" s="48" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="23" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H55" s="23" t="s">
         <v>27</v>
@@ -13129,20 +13138,20 @@
     <row r="56" spans="1:13" ht="19.5">
       <c r="A56" s="94"/>
       <c r="B56" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C56" s="48" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="23" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H56" s="23" t="s">
         <v>27</v>
@@ -13156,20 +13165,20 @@
     <row r="57" spans="1:13" ht="19.5">
       <c r="A57" s="94"/>
       <c r="B57" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C57" s="48" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E57" s="23"/>
       <c r="F57" s="23" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H57" s="23" t="s">
         <v>27</v>
@@ -13185,20 +13194,20 @@
     <row r="58" spans="1:13" ht="19.5">
       <c r="A58" s="94"/>
       <c r="B58" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C58" s="48" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E58" s="23"/>
       <c r="F58" s="23" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H58" s="23" t="s">
         <v>27</v>
@@ -13212,17 +13221,17 @@
     <row r="59" spans="1:13" ht="19.5">
       <c r="A59" s="94"/>
       <c r="B59" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C59" s="48" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E59" s="23"/>
       <c r="F59" s="23" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G59" s="21" t="s">
         <v>33</v>
@@ -13239,23 +13248,23 @@
     <row r="60" spans="1:13" ht="19.5">
       <c r="A60" s="94"/>
       <c r="B60" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C60" s="48" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E60" s="23"/>
       <c r="F60" s="23" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G60" s="21" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I60" s="113"/>
       <c r="J60" s="23"/>
@@ -13268,23 +13277,23 @@
     <row r="61" spans="1:13" ht="19.5">
       <c r="A61" s="94"/>
       <c r="B61" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="23" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I61" s="113"/>
       <c r="J61" s="23"/>
@@ -13297,23 +13306,23 @@
     <row r="62" spans="1:13" ht="19.5">
       <c r="A62" s="94"/>
       <c r="B62" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C62" s="48" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E62" s="23"/>
       <c r="F62" s="23" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I62" s="113"/>
       <c r="J62" s="23"/>
@@ -13326,23 +13335,23 @@
     <row r="63" spans="1:13" ht="19.5">
       <c r="A63" s="94"/>
       <c r="B63" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="23" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G63" s="21" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I63" s="113"/>
       <c r="J63" s="23"/>
@@ -13355,23 +13364,23 @@
     <row r="64" spans="1:13" ht="19.5">
       <c r="A64" s="94"/>
       <c r="B64" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C64" s="48" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="23" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G64" s="21" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I64" s="113"/>
       <c r="J64" s="23"/>
@@ -13384,23 +13393,23 @@
     <row r="65" spans="1:13" ht="19.5">
       <c r="A65" s="94"/>
       <c r="B65" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C65" s="48" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="23" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G65" s="21" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I65" s="113"/>
       <c r="J65" s="23"/>
@@ -13413,20 +13422,20 @@
     <row r="66" spans="1:13" ht="19.5">
       <c r="A66" s="94"/>
       <c r="B66" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C66" s="48" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E66" s="23"/>
       <c r="F66" s="23" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G66" s="21" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H66" s="23" t="s">
         <v>27</v>
@@ -13440,20 +13449,20 @@
     <row r="67" spans="1:13" ht="19.5">
       <c r="A67" s="94"/>
       <c r="B67" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E67" s="23"/>
       <c r="F67" s="23" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G67" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>27</v>
@@ -13469,20 +13478,20 @@
     <row r="68" spans="1:13" ht="19.5">
       <c r="A68" s="94"/>
       <c r="B68" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C68" s="48" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E68" s="23"/>
       <c r="F68" s="23" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G68" s="21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H68" s="23" t="s">
         <v>27</v>
@@ -13498,26 +13507,26 @@
     <row r="69" spans="1:13" ht="37.5">
       <c r="A69" s="94"/>
       <c r="B69" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C69" s="174" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D69" s="176" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E69" s="150"/>
       <c r="F69" s="150" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G69" s="175" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H69" s="150" t="s">
         <v>27</v>
       </c>
       <c r="I69" s="150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J69" s="150"/>
       <c r="K69" s="177"/>
@@ -13529,26 +13538,26 @@
     <row r="70" spans="1:13" ht="19.5">
       <c r="A70" s="94"/>
       <c r="B70" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C70" s="48" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E70" s="23"/>
       <c r="F70" s="23" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G70" s="21" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H70" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I70" s="114" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J70" s="23"/>
       <c r="K70" s="50"/>
@@ -13560,24 +13569,24 @@
     <row r="71" spans="1:13" ht="19.5">
       <c r="A71" s="94"/>
       <c r="B71" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C71" s="48" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D71" s="23"/>
       <c r="E71" s="23"/>
       <c r="F71" s="23" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G71" s="21" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H71" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I71" s="114" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J71" s="23"/>
       <c r="K71" s="50"/>
@@ -13589,26 +13598,26 @@
     <row r="72" spans="1:13" ht="19.5">
       <c r="A72" s="94"/>
       <c r="B72" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E72" s="23"/>
       <c r="F72" s="23" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G72" s="21" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H72" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I72" s="114" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J72" s="23"/>
       <c r="K72" s="50"/>
@@ -13620,26 +13629,26 @@
     <row r="73" spans="1:13" ht="19.5">
       <c r="A73" s="94"/>
       <c r="B73" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C73" s="48" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E73" s="23"/>
       <c r="F73" s="23" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G73" s="21" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H73" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I73" s="114" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J73" s="23"/>
       <c r="K73" s="50"/>
@@ -13651,20 +13660,20 @@
     <row r="74" spans="1:13" ht="37.5">
       <c r="A74" s="94"/>
       <c r="B74" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C74" s="174" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D74" s="176" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E74" s="150"/>
       <c r="F74" s="150" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G74" s="175" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H74" s="150" t="s">
         <v>27</v>
@@ -13680,17 +13689,17 @@
     <row r="75" spans="1:13" ht="19.5">
       <c r="A75" s="94"/>
       <c r="B75" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C75" s="48" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E75" s="23"/>
       <c r="F75" s="23" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G75" s="21" t="s">
         <v>297</v>
@@ -13707,20 +13716,20 @@
     <row r="76" spans="1:13" ht="19.5">
       <c r="A76" s="94"/>
       <c r="B76" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C76" s="48" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E76" s="23"/>
       <c r="F76" s="23" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G76" s="21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H76" s="23" t="s">
         <v>27</v>
@@ -13734,20 +13743,20 @@
     <row r="77" spans="1:13" ht="19.5">
       <c r="A77" s="94"/>
       <c r="B77" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C77" s="48" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E77" s="23"/>
       <c r="F77" s="23" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G77" s="21" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H77" s="23" t="s">
         <v>27</v>
@@ -13763,20 +13772,20 @@
     <row r="78" spans="1:13" ht="19.5">
       <c r="A78" s="94"/>
       <c r="B78" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C78" s="48" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E78" s="23"/>
       <c r="F78" s="23" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G78" s="21" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H78" s="23" t="s">
         <v>27</v>
@@ -13792,20 +13801,20 @@
     <row r="79" spans="1:13" ht="19.5">
       <c r="A79" s="94"/>
       <c r="B79" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C79" s="48" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="23" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G79" s="21" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H79" s="23" t="s">
         <v>27</v>
@@ -13821,26 +13830,26 @@
     <row r="80" spans="1:13" ht="37.5">
       <c r="A80" s="94"/>
       <c r="B80" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C80" s="174" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D80" s="176" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E80" s="150"/>
       <c r="F80" s="150" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G80" s="175" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H80" s="150" t="s">
         <v>27</v>
       </c>
       <c r="I80" s="150" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J80" s="150"/>
       <c r="K80" s="177"/>
@@ -13852,20 +13861,20 @@
     <row r="81" spans="1:13" ht="19.5">
       <c r="A81" s="94"/>
       <c r="B81" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C81" s="48" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E81" s="23"/>
       <c r="F81" s="23" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G81" s="21" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H81" s="23" t="s">
         <v>27</v>
@@ -13881,26 +13890,26 @@
     <row r="82" spans="1:13" ht="37.5">
       <c r="A82" s="94"/>
       <c r="B82" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C82" s="174" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D82" s="176" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E82" s="150"/>
       <c r="F82" s="150" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G82" s="175" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H82" s="150" t="s">
         <v>27</v>
       </c>
       <c r="I82" s="150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J82" s="150"/>
       <c r="K82" s="177"/>
@@ -13912,26 +13921,26 @@
     <row r="83" spans="1:13" ht="19.5">
       <c r="A83" s="94"/>
       <c r="B83" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C83" s="48" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E83" s="23"/>
       <c r="F83" s="23" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G83" s="21" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H83" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I83" s="114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J83" s="23"/>
       <c r="K83" s="50"/>
@@ -13943,26 +13952,26 @@
     <row r="84" spans="1:13" ht="19.5">
       <c r="A84" s="94"/>
       <c r="B84" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C84" s="48" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E84" s="23"/>
       <c r="F84" s="23" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G84" s="21" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H84" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I84" s="114" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J84" s="23"/>
       <c r="K84" s="50"/>
@@ -13974,26 +13983,26 @@
     <row r="85" spans="1:13" ht="19.5">
       <c r="A85" s="94"/>
       <c r="B85" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C85" s="48" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E85" s="23"/>
       <c r="F85" s="23" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G85" s="21" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H85" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I85" s="114" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J85" s="23"/>
       <c r="K85" s="50"/>
@@ -14005,26 +14014,26 @@
     <row r="86" spans="1:13" ht="19.5">
       <c r="A86" s="94"/>
       <c r="B86" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E86" s="23"/>
       <c r="F86" s="23" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G86" s="21" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H86" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I86" s="114" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J86" s="23"/>
       <c r="K86" s="50"/>
@@ -14036,20 +14045,20 @@
     <row r="87" spans="1:13" ht="19.5">
       <c r="A87" s="94"/>
       <c r="B87" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="23" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G87" s="21" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H87" s="23" t="s">
         <v>27</v>
@@ -14065,20 +14074,20 @@
     <row r="88" spans="1:13" ht="19.5">
       <c r="A88" s="94"/>
       <c r="B88" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C88" s="48" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E88" s="23"/>
       <c r="F88" s="23" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G88" s="21" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H88" s="23" t="s">
         <v>27</v>
@@ -14094,26 +14103,26 @@
     <row r="89" spans="1:13" ht="37.5">
       <c r="A89" s="94"/>
       <c r="B89" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C89" s="174" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D89" s="176" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E89" s="150"/>
       <c r="F89" s="150" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G89" s="175" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H89" s="150" t="s">
         <v>27</v>
       </c>
       <c r="I89" s="150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J89" s="150"/>
       <c r="K89" s="177"/>
@@ -14125,26 +14134,26 @@
     <row r="90" spans="1:13" ht="19.5">
       <c r="A90" s="94"/>
       <c r="B90" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C90" s="48" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E90" s="23"/>
       <c r="F90" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G90" s="21" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H90" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I90" s="114" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J90" s="23"/>
       <c r="K90" s="50"/>
@@ -14156,26 +14165,26 @@
     <row r="91" spans="1:13" ht="19.5">
       <c r="A91" s="94"/>
       <c r="B91" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C91" s="48" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E91" s="23"/>
       <c r="F91" s="23" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G91" s="21" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H91" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I91" s="114" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J91" s="23"/>
       <c r="K91" s="50"/>
@@ -14187,26 +14196,26 @@
     <row r="92" spans="1:13" ht="19.5">
       <c r="A92" s="94"/>
       <c r="B92" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C92" s="48" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E92" s="23"/>
       <c r="F92" s="23" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G92" s="21" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H92" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I92" s="114" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J92" s="23"/>
       <c r="K92" s="50"/>
@@ -14218,26 +14227,26 @@
     <row r="93" spans="1:13" ht="37.5">
       <c r="A93" s="94"/>
       <c r="B93" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C93" s="174" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D93" s="176" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E93" s="150"/>
       <c r="F93" s="150" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G93" s="175" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H93" s="150" t="s">
         <v>27</v>
       </c>
       <c r="I93" s="150" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J93" s="150"/>
       <c r="K93" s="177"/>
@@ -14249,26 +14258,26 @@
     <row r="94" spans="1:13" ht="19.5">
       <c r="A94" s="94"/>
       <c r="B94" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C94" s="48" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D94" s="23" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E94" s="23"/>
       <c r="F94" s="23" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G94" s="21" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H94" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I94" s="114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J94" s="23"/>
       <c r="K94" s="50"/>
@@ -14280,26 +14289,26 @@
     <row r="95" spans="1:13" ht="19.5">
       <c r="A95" s="94"/>
       <c r="B95" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C95" s="48" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E95" s="23"/>
       <c r="F95" s="23" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G95" s="21" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H95" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I95" s="114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J95" s="23"/>
       <c r="K95" s="50"/>
@@ -14311,25 +14320,25 @@
     <row r="96" spans="1:13" ht="37.5">
       <c r="A96" s="94"/>
       <c r="B96" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C96" s="174" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D96" s="150"/>
       <c r="E96" s="150"/>
       <c r="F96" s="150" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G96" s="175" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H96" s="150" t="s">
         <v>27</v>
       </c>
       <c r="I96" s="150"/>
       <c r="J96" s="176" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K96" s="50"/>
       <c r="L96" s="118" t="b">
@@ -14340,25 +14349,25 @@
     <row r="97" spans="1:13" ht="37.5">
       <c r="A97" s="94"/>
       <c r="B97" s="173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C97" s="174" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D97" s="150"/>
       <c r="E97" s="150"/>
       <c r="F97" s="150" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G97" s="175" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H97" s="150" t="s">
         <v>27</v>
       </c>
       <c r="I97" s="150"/>
       <c r="J97" s="176" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="K97" s="50"/>
       <c r="L97" s="118" t="b">
@@ -14369,20 +14378,20 @@
     <row r="98" spans="1:13" ht="19.5">
       <c r="A98" s="94"/>
       <c r="B98" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C98" s="48" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E98" s="23"/>
       <c r="F98" s="23" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G98" s="21" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H98" s="23" t="s">
         <v>27</v>
@@ -14398,26 +14407,26 @@
     <row r="99" spans="1:13" ht="19.5">
       <c r="A99" s="94"/>
       <c r="B99" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E99" s="23"/>
       <c r="F99" s="23" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G99" s="21" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H99" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I99" s="114" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J99" s="23"/>
       <c r="K99" s="50"/>
@@ -14429,26 +14438,26 @@
     <row r="100" spans="1:13" ht="19.5">
       <c r="A100" s="94"/>
       <c r="B100" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C100" s="48" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E100" s="23"/>
       <c r="F100" s="23" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H100" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I100" s="114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J100" s="23"/>
       <c r="K100" s="50"/>
@@ -14460,26 +14469,26 @@
     <row r="101" spans="1:13" ht="19.5">
       <c r="A101" s="94"/>
       <c r="B101" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C101" s="48" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E101" s="23"/>
       <c r="F101" s="23" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H101" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I101" s="114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J101" s="23"/>
       <c r="K101" s="50"/>
@@ -14491,26 +14500,26 @@
     <row r="102" spans="1:13" ht="19.5">
       <c r="A102" s="94"/>
       <c r="B102" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C102" s="48" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E102" s="23"/>
       <c r="F102" s="23" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G102" s="21" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H102" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I102" s="114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J102" s="23"/>
       <c r="K102" s="50"/>
@@ -14522,20 +14531,20 @@
     <row r="103" spans="1:13" ht="19.5">
       <c r="A103" s="94"/>
       <c r="B103" s="112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C103" s="48" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E103" s="23"/>
       <c r="F103" s="23" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G103" s="21" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H103" s="23" t="s">
         <v>27</v>
@@ -14582,7 +14591,7 @@
   <sheetData>
     <row r="2" spans="1:6" ht="18.75" customHeight="1">
       <c r="A2" s="143" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B2" s="99" t="s">
         <v>282</v>
@@ -14598,13 +14607,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="100" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B3" s="101" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="217" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D3" s="218"/>
       <c r="E3" s="219"/>
@@ -14636,10 +14645,10 @@
         <v>281</v>
       </c>
       <c r="C5" s="107" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D5" s="108" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E5" s="108" t="s">
         <v>291</v>
@@ -14650,7 +14659,7 @@
       <c r="A6" s="145"/>
       <c r="B6" s="104"/>
       <c r="C6" s="107" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D6" s="108" t="s">
         <v>292</v>
@@ -14667,10 +14676,10 @@
         <v>293</v>
       </c>
       <c r="D7" s="108" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E7" s="109" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F7" s="109"/>
     </row>
@@ -14681,10 +14690,10 @@
         <v>293</v>
       </c>
       <c r="D8" s="108" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E8" s="109" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F8" s="109"/>
     </row>
@@ -14695,10 +14704,10 @@
         <v>294</v>
       </c>
       <c r="D9" s="108" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E9" s="108" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F9" s="109"/>
     </row>
@@ -14706,21 +14715,21 @@
       <c r="A10" s="145"/>
       <c r="B10" s="104"/>
       <c r="C10" s="109" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F10" s="109" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.5">
       <c r="A13" s="143" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B13" s="99" t="s">
         <v>282</v>
@@ -14742,7 +14751,7 @@
         <v>38</v>
       </c>
       <c r="C14" s="217" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D14" s="218"/>
       <c r="E14" s="219"/>
@@ -14774,10 +14783,10 @@
         <v>281</v>
       </c>
       <c r="C16" s="107" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D16" s="108" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E16" s="108" t="s">
         <v>291</v>
@@ -14790,7 +14799,7 @@
         <v>281</v>
       </c>
       <c r="C17" s="107" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D17" s="108" t="s">
         <v>292</v>
@@ -14807,10 +14816,10 @@
         <v>293</v>
       </c>
       <c r="D18" s="108" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E18" s="109" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F18" s="109"/>
     </row>
@@ -14821,13 +14830,13 @@
         <v>293</v>
       </c>
       <c r="D19" s="108" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E19" s="109" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F19" s="109" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="185.25" customHeight="1">
@@ -14837,13 +14846,13 @@
         <v>294</v>
       </c>
       <c r="D20" s="108" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E20" s="108" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F20" s="109" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="184.5" customHeight="1">
@@ -14853,13 +14862,13 @@
         <v>293</v>
       </c>
       <c r="D21" s="108" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E21" s="109" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F21" s="109" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="185.25" customHeight="1">
@@ -14869,13 +14878,13 @@
         <v>293</v>
       </c>
       <c r="D22" s="108" t="s">
-        <v>718</v>
+        <v>777</v>
       </c>
       <c r="E22" s="109" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="F22" s="109" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -14886,7 +14895,7 @@
     </row>
     <row r="24" spans="1:6" ht="19.5">
       <c r="A24" s="143" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B24" s="99" t="s">
         <v>282</v>
@@ -14908,7 +14917,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="217" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D25" s="218"/>
       <c r="E25" s="219"/>
@@ -14942,10 +14951,10 @@
         <v>281</v>
       </c>
       <c r="C27" s="107" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D27" s="108" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E27" s="108" t="s">
         <v>291</v>
@@ -14958,7 +14967,7 @@
         <v>281</v>
       </c>
       <c r="C28" s="107" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D28" s="108" t="s">
         <v>292</v>
@@ -14975,10 +14984,10 @@
         <v>293</v>
       </c>
       <c r="D29" s="108" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E29" s="109" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F29" s="109"/>
     </row>
@@ -14989,7 +14998,7 @@
         <v>293</v>
       </c>
       <c r="D30" s="108" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E30" s="109" t="s">
         <v>762</v>
@@ -15003,13 +15012,13 @@
         <v>293</v>
       </c>
       <c r="D31" s="108" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E31" s="109" t="s">
         <v>763</v>
       </c>
       <c r="F31" s="109" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="114" customHeight="1">
@@ -15019,13 +15028,13 @@
         <v>293</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E32" s="109" t="s">
         <v>764</v>
       </c>
       <c r="F32" s="109" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="191.25" customHeight="1">
@@ -15035,7 +15044,7 @@
         <v>294</v>
       </c>
       <c r="D33" s="108" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E33" s="108" t="s">
         <v>765</v>
@@ -15046,10 +15055,10 @@
       <c r="A34" s="146"/>
       <c r="B34" s="149"/>
       <c r="C34" s="109" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D34" s="108" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E34" s="108" t="s">
         <v>766</v>
@@ -15062,37 +15071,37 @@
       <c r="A35" s="146"/>
       <c r="B35" s="149"/>
       <c r="C35" s="109" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D35" s="108" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E35" s="108" t="s">
         <v>767</v>
       </c>
       <c r="F35" s="109" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="205.5" customHeight="1">
       <c r="A36" s="146"/>
       <c r="B36" s="149"/>
       <c r="C36" s="109" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D36" s="108" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E36" s="108" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="F36" s="109" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="19.5">
       <c r="A39" s="143" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B39" s="99" t="s">
         <v>282</v>
@@ -15114,7 +15123,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="217" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D40" s="218"/>
       <c r="E40" s="219"/>
@@ -15148,10 +15157,10 @@
         <v>281</v>
       </c>
       <c r="C42" s="107" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D42" s="108" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E42" s="108" t="s">
         <v>291</v>
@@ -15164,7 +15173,7 @@
         <v>281</v>
       </c>
       <c r="C43" s="107" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D43" s="108" t="s">
         <v>292</v>
@@ -15181,10 +15190,10 @@
         <v>293</v>
       </c>
       <c r="D44" s="108" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E44" s="109" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F44" s="109"/>
     </row>
@@ -15195,10 +15204,10 @@
         <v>293</v>
       </c>
       <c r="D45" s="108" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E45" s="109" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F45" s="109"/>
     </row>
@@ -15209,13 +15218,13 @@
         <v>293</v>
       </c>
       <c r="D46" s="108" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E46" s="109" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F46" s="109" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="121.5" customHeight="1">
@@ -15227,13 +15236,13 @@
         <v>293</v>
       </c>
       <c r="D47" s="108" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E47" s="109" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F47" s="109" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="209.25" customHeight="1">
@@ -15245,10 +15254,10 @@
         <v>294</v>
       </c>
       <c r="D48" s="108" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E48" s="108" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F48" s="109"/>
     </row>
@@ -15258,13 +15267,13 @@
         <v>281</v>
       </c>
       <c r="C49" s="109" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D49" s="108" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E49" s="108" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F49" s="109" t="s">
         <v>761</v>
@@ -15276,16 +15285,16 @@
         <v>281</v>
       </c>
       <c r="C50" s="109" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D50" s="108" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E50" s="108" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F50" s="109" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="210" customHeight="1">
@@ -15294,16 +15303,16 @@
         <v>281</v>
       </c>
       <c r="C51" s="109" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D51" s="108" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E51" s="108" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F51" s="109" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="99" spans="9:13">
@@ -15391,7 +15400,7 @@
     </row>
     <row r="2" spans="1:8" ht="93.75">
       <c r="A2" s="45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="44" t="s">
@@ -15415,13 +15424,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="114" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>27</v>
@@ -15429,21 +15438,21 @@
       <c r="E3" s="114"/>
       <c r="F3" s="23"/>
       <c r="G3" s="23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>27</v>
@@ -15451,21 +15460,21 @@
       <c r="E4" s="114"/>
       <c r="F4" s="23"/>
       <c r="G4" s="116" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>27</v>
@@ -15473,19 +15482,19 @@
       <c r="E5" s="114"/>
       <c r="F5" s="23"/>
       <c r="G5" s="116" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="23" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>27</v>
@@ -15493,19 +15502,19 @@
       <c r="E6" s="114"/>
       <c r="F6" s="23"/>
       <c r="G6" s="117" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" ht="56.25">
       <c r="A7" s="150" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B7" s="150" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C7" s="150" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D7" s="150" t="s">
         <v>249</v>
@@ -15513,21 +15522,21 @@
       <c r="E7" s="150"/>
       <c r="F7" s="150"/>
       <c r="G7" s="151" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="37.5">
       <c r="A8" s="150" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B8" s="150" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C8" s="150" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D8" s="150" t="s">
         <v>27</v>
@@ -15535,10 +15544,10 @@
       <c r="E8" s="150"/>
       <c r="F8" s="150"/>
       <c r="G8" s="151" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -15608,7 +15617,7 @@
         <v>45772</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>776</v>
+        <v>301</v>
       </c>
       <c r="D5" s="69"/>
       <c r="E5" s="70" t="s">
